--- a/data/Ascona/investment_decision/Ascona_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/Ascona_SFH_2005-2014_investment_decision.xlsx
@@ -440,52 +440,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>21.63846974340451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,25 +505,25 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>21.63846974340451</v>
       </c>
       <c r="G2" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>21.63846974340451</v>
       </c>
       <c r="I2" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>21.63846974340451</v>
       </c>
       <c r="K2" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>109.5802098818709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,25 +542,25 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>107.2993600100631</v>
       </c>
       <c r="G3" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>109.5802098818709</v>
       </c>
       <c r="I3" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>107.2993600100631</v>
       </c>
       <c r="K3" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
     </row>
     <row r="4">
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>107.8853432209855</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,25 +579,25 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.7476915709111</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="G4" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="H4" t="n">
-        <v>107.8853432209855</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="I4" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="J4" t="n">
-        <v>107.7476915709111</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="K4" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>108.9394520808885</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,25 +616,25 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="F5" t="n">
-        <v>108.79933032505</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="G5" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="H5" t="n">
-        <v>108.9394520808885</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="I5" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="J5" t="n">
-        <v>108.79933032505</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="K5" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>108.9394520808885</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,25 +653,25 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="F6" t="n">
-        <v>108.7993303250501</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="G6" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9394520808885</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="I6" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
       <c r="J6" t="n">
-        <v>108.7993303250501</v>
+        <v>109.7017482814657</v>
       </c>
       <c r="K6" t="n">
-        <v>19391.12877274079</v>
+        <v>19408.05189577003</v>
       </c>
     </row>
     <row r="7">
@@ -690,25 +690,25 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>29.08669315911119</v>
+        <v>16.578148974153</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>29.08669315911119</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>16.56369342466285</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16.56369342466285</v>
+        <v>16.578148974153</v>
       </c>
     </row>
     <row r="8">
@@ -727,25 +727,25 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>29.08669315911119</v>
+        <v>20.18031800472211</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>29.08669315911119</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>20.1627214934289</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20.1627214934289</v>
+        <v>20.18031800472211</v>
       </c>
     </row>
     <row r="9">
@@ -764,25 +764,25 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>29.08669315911119</v>
+        <v>21.65587507166034</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>29.08669315911119</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>21.63699192768939</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21.63699192768939</v>
+        <v>21.65587507166034</v>
       </c>
     </row>
     <row r="10">
@@ -801,25 +801,25 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>29.08669315911119</v>
+        <v>22.44462784992312</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>29.08669315911119</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>22.42505694190568</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.42505694190568</v>
+        <v>22.44462784992312</v>
       </c>
     </row>
     <row r="11">
@@ -838,25 +838,25 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>29.08669315911119</v>
+        <v>22.93749663065686</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>29.08669315911119</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>22.91749595879407</v>
+        <v>29.11207784365505</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>22.91749595879407</v>
+        <v>22.93749663065686</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.007126851896470589</v>
+        <v>0.008252144301176472</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007126851896470589</v>
+        <v>0.008252144301176472</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007126851896470589</v>
+        <v>0.008252144301176472</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.007126851896470589</v>
+        <v>0.008252144301176472</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.007520058331023649</v>
+        <v>0.008627241769411768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007520058331023649</v>
+        <v>0.008627241769411768</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.007520058331023649</v>
+        <v>0.008627241769411768</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.007520058331023646</v>
+        <v>0.008627241769411768</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01004608652365032</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01003930915064056</v>
+        <v>0.009002339237647058</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.04332084431076671</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04692132372220224</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="G19" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04332084431076752</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="I19" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04692132372220077</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="K19" t="n">
         <v>6.695489808000001</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.04332084431076671</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04692132372220224</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="G20" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.04332084431076752</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="I20" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04692132372220077</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="K20" t="n">
         <v>6.695489808000001</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.04332084431076671</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04692132372220224</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="G21" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04332084431076736</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="I21" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.04692132372220077</v>
+        <v>4.181033780000001</v>
       </c>
       <c r="K21" t="n">
         <v>6.695489808000001</v>
@@ -1985,7 +1985,7 @@
         <v>0.01</v>
       </c>
       <c r="E42" t="n">
-        <v>22.06667889117543</v>
+        <v>12.79481137712283</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>12.79481137712283</v>
+        <v>22.06667889117543</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0.01</v>
       </c>
       <c r="E43" t="n">
-        <v>22.06667889117543</v>
+        <v>15.55641955585784</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>15.55641955585784</v>
+        <v>22.06667889117543</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         <v>0.01</v>
       </c>
       <c r="E44" t="n">
-        <v>22.06667889117543</v>
+        <v>16.69372711176654</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>16.69372711176654</v>
+        <v>22.06667889117543</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0.01</v>
       </c>
       <c r="E45" t="n">
-        <v>22.06667889117543</v>
+        <v>17.31024064161294</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>17.31024064161294</v>
+        <v>22.06667889117543</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>0.01</v>
       </c>
       <c r="E46" t="n">
-        <v>22.06667889117543</v>
+        <v>17.7020365223083</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>17.7020365223083</v>
+        <v>22.06667889117543</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2170,25 +2170,25 @@
         <v>0.017</v>
       </c>
       <c r="E47" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="48">
@@ -2207,25 +2207,25 @@
         <v>0.017</v>
       </c>
       <c r="E48" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="49">
@@ -2244,25 +2244,25 @@
         <v>0.017</v>
       </c>
       <c r="E49" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="50">
@@ -2281,25 +2281,25 @@
         <v>0.017</v>
       </c>
       <c r="E50" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="51">
@@ -2318,25 +2318,25 @@
         <v>0.017</v>
       </c>
       <c r="E51" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="52">
@@ -2355,25 +2355,25 @@
         <v>0.017</v>
       </c>
       <c r="E52" t="n">
-        <v>29.6846201766412</v>
+        <v>9.791321608834714</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>9.313696164501316</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>9.313696164501316</v>
+        <v>9.791321608834714</v>
       </c>
     </row>
     <row r="53">
@@ -2392,25 +2392,25 @@
         <v>0.017</v>
       </c>
       <c r="E53" t="n">
-        <v>29.6846201766412</v>
+        <v>12.88031855625539</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.4540405107664842</v>
       </c>
       <c r="G53" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>12.25201033399903</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.4540405107664842</v>
       </c>
       <c r="K53" t="n">
-        <v>12.25201033399903</v>
+        <v>12.88031855625539</v>
       </c>
     </row>
     <row r="54">
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>4.383326583017678</v>
+        <v>6.074260917059727</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,25 +2429,25 @@
         <v>0.017</v>
       </c>
       <c r="E54" t="n">
-        <v>29.6846201766412</v>
+        <v>14.25692762004364</v>
       </c>
       <c r="F54" t="n">
-        <v>4.111978320203356</v>
+        <v>6.510329549934112</v>
       </c>
       <c r="G54" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H54" t="n">
-        <v>4.383326583017677</v>
+        <v>6.074260917059727</v>
       </c>
       <c r="I54" t="n">
-        <v>13.56146773613907</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J54" t="n">
-        <v>4.111978320203356</v>
+        <v>6.510329549934112</v>
       </c>
       <c r="K54" t="n">
-        <v>13.56146773613907</v>
+        <v>14.25692762004364</v>
       </c>
     </row>
     <row r="55">
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.83991644716246</v>
+        <v>6.728574331135669</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,25 +2466,25 @@
         <v>0.017</v>
       </c>
       <c r="E55" t="n">
-        <v>29.6846201766412</v>
+        <v>14.99985363935659</v>
       </c>
       <c r="F55" t="n">
-        <v>5.340269128129346</v>
+        <v>7.040347518358541</v>
       </c>
       <c r="G55" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H55" t="n">
-        <v>5.83991644716246</v>
+        <v>6.728574331135669</v>
       </c>
       <c r="I55" t="n">
-        <v>14.268153461827</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J55" t="n">
-        <v>5.340269128129346</v>
+        <v>7.040347518358541</v>
       </c>
       <c r="K55" t="n">
-        <v>14.268153461827</v>
+        <v>14.99985363935659</v>
       </c>
     </row>
     <row r="56">
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.83991644716246</v>
+        <v>7.126228968529673</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,25 +2503,25 @@
         <v>0.017</v>
       </c>
       <c r="E56" t="n">
-        <v>29.6846201766412</v>
+        <v>15.45846662840667</v>
       </c>
       <c r="F56" t="n">
-        <v>5.340269128129345</v>
+        <v>7.606583658544579</v>
       </c>
       <c r="G56" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H56" t="n">
-        <v>5.83991644716246</v>
+        <v>7.126228968529673</v>
       </c>
       <c r="I56" t="n">
-        <v>14.70439508555756</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J56" t="n">
-        <v>5.340269128129345</v>
+        <v>7.606583658544579</v>
       </c>
       <c r="K56" t="n">
-        <v>14.70439508555756</v>
+        <v>15.45846662840667</v>
       </c>
     </row>
     <row r="57">
@@ -2540,25 +2540,25 @@
         <v>0.017</v>
       </c>
       <c r="E57" t="n">
-        <v>29.6846201766412</v>
+        <v>9.791321608834714</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>9.313696164501316</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>9.313696164501316</v>
+        <v>9.791321608834714</v>
       </c>
     </row>
     <row r="58">
@@ -2577,25 +2577,25 @@
         <v>0.017</v>
       </c>
       <c r="E58" t="n">
-        <v>29.6846201766412</v>
+        <v>12.88031855625539</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>12.25201033399903</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>12.25201033399903</v>
+        <v>12.88031855625539</v>
       </c>
     </row>
     <row r="59">
@@ -2614,25 +2614,25 @@
         <v>0.017</v>
       </c>
       <c r="E59" t="n">
-        <v>29.6846201766412</v>
+        <v>14.25692762004364</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>13.56146773613907</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>13.56146773613907</v>
+        <v>14.25692762004364</v>
       </c>
     </row>
     <row r="60">
@@ -2651,25 +2651,25 @@
         <v>0.017</v>
       </c>
       <c r="E60" t="n">
-        <v>29.6846201766412</v>
+        <v>14.99985363935659</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>14.268153461827</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>14.268153461827</v>
+        <v>14.99985363935659</v>
       </c>
     </row>
     <row r="61">
@@ -2688,25 +2688,25 @@
         <v>0.017</v>
       </c>
       <c r="E61" t="n">
-        <v>29.6846201766412</v>
+        <v>15.45846662840667</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>14.70439508555756</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>14.70439508555756</v>
+        <v>15.45846662840667</v>
       </c>
     </row>
     <row r="62">
@@ -2725,25 +2725,25 @@
         <v>0.017</v>
       </c>
       <c r="E62" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="63">
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>0.5663190004483585</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
         <v>0.017</v>
       </c>
       <c r="E63" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.5663190004483585</v>
       </c>
       <c r="I63" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="64">
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>3.735036053565671</v>
+        <v>6.489377089279921</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
         <v>0.017</v>
       </c>
       <c r="E64" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F64" t="n">
-        <v>4.009420749837517</v>
+        <v>5.890717101904373</v>
       </c>
       <c r="G64" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H64" t="n">
-        <v>3.735036053565673</v>
+        <v>6.489377089279921</v>
       </c>
       <c r="I64" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J64" t="n">
-        <v>4.009420749837518</v>
+        <v>5.890717101904373</v>
       </c>
       <c r="K64" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="65">
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>4.255193788099499</v>
+        <v>7.835063675203981</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
         <v>0.017</v>
       </c>
       <c r="E65" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F65" t="n">
-        <v>4.757932028217285</v>
+        <v>7.360699133479946</v>
       </c>
       <c r="G65" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H65" t="n">
-        <v>4.255193788099499</v>
+        <v>7.835063675203981</v>
       </c>
       <c r="I65" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J65" t="n">
-        <v>4.757932028217285</v>
+        <v>7.360699133479946</v>
       </c>
       <c r="K65" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="66">
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.255193788099499</v>
+        <v>9.545675405931656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,25 +2873,25 @@
         <v>0.017</v>
       </c>
       <c r="E66" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F66" t="n">
-        <v>4.757932028217285</v>
+        <v>9.065320715916751</v>
       </c>
       <c r="G66" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H66" t="n">
-        <v>4.255193788099499</v>
+        <v>9.545675405931656</v>
       </c>
       <c r="I66" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J66" t="n">
-        <v>4.757932028217285</v>
+        <v>9.065320715916751</v>
       </c>
       <c r="K66" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="67">
@@ -2910,25 +2910,25 @@
         <v>0.017</v>
       </c>
       <c r="E67" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="68">
@@ -2947,25 +2947,25 @@
         <v>0.017</v>
       </c>
       <c r="E68" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="69">
@@ -2984,25 +2984,25 @@
         <v>0.017</v>
       </c>
       <c r="E69" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="70">
@@ -3021,25 +3021,25 @@
         <v>0.017</v>
       </c>
       <c r="E70" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="71">
@@ -3058,25 +3058,25 @@
         <v>0.017</v>
       </c>
       <c r="E71" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="72">
@@ -3095,25 +3095,25 @@
         <v>0.017</v>
       </c>
       <c r="E72" t="n">
-        <v>29.6846201766412</v>
+        <v>0.9658235990298158</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9187102527356787</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9187102527356787</v>
+        <v>0.9658235990298158</v>
       </c>
     </row>
     <row r="73">
@@ -3132,25 +3132,25 @@
         <v>0.017</v>
       </c>
       <c r="E73" t="n">
-        <v>29.6846201766412</v>
+        <v>1.495821401433555</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1.42285450380265</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.42285450380265</v>
+        <v>1.495821401433555</v>
       </c>
     </row>
     <row r="74">
@@ -3169,25 +3169,25 @@
         <v>0.017</v>
       </c>
       <c r="E74" t="n">
-        <v>29.6846201766412</v>
+        <v>1.845230926841906</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1.755219662117911</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.755219662117911</v>
+        <v>1.845230926841906</v>
       </c>
     </row>
     <row r="75">
@@ -3206,25 +3206,25 @@
         <v>0.017</v>
       </c>
       <c r="E75" t="n">
-        <v>29.6846201766412</v>
+        <v>2.09966409142957</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1.99724145282325</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.99724145282325</v>
+        <v>2.09966409142957</v>
       </c>
     </row>
     <row r="76">
@@ -3243,25 +3243,25 @@
         <v>0.017</v>
       </c>
       <c r="E76" t="n">
-        <v>29.6846201766412</v>
+        <v>2.296615036807896</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2.18458503501239</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2.18458503501239</v>
+        <v>2.296615036807896</v>
       </c>
     </row>
     <row r="77">
@@ -3280,25 +3280,25 @@
         <v>0.017</v>
       </c>
       <c r="E77" t="n">
-        <v>29.6846201766412</v>
+        <v>0.9658235990298158</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9187102527356787</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9187102527356787</v>
+        <v>0.9658235990298158</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,25 +3317,25 @@
         <v>0.017</v>
       </c>
       <c r="E78" t="n">
-        <v>29.6846201766412</v>
+        <v>1.495821401433555</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="G78" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="I78" t="n">
-        <v>1.42285450380265</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="K78" t="n">
-        <v>1.42285450380265</v>
+        <v>1.495821401433555</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
         <v>0.017</v>
       </c>
       <c r="E79" t="n">
-        <v>29.6846201766412</v>
+        <v>1.845230926841906</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="G79" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="I79" t="n">
-        <v>1.755219662117911</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="K79" t="n">
-        <v>1.755219662117911</v>
+        <v>1.845230926841906</v>
       </c>
     </row>
     <row r="80">
@@ -3380,7 +3380,7 @@
         <v>51502</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3391,25 +3391,25 @@
         <v>0.017</v>
       </c>
       <c r="E80" t="n">
-        <v>29.6846201766412</v>
+        <v>2.09966409142957</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="G80" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="I80" t="n">
-        <v>1.99724145282325</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="K80" t="n">
-        <v>1.99724145282325</v>
+        <v>2.09966409142957</v>
       </c>
     </row>
     <row r="81">
@@ -3428,25 +3428,25 @@
         <v>0.017</v>
       </c>
       <c r="E81" t="n">
-        <v>29.6846201766412</v>
+        <v>2.296615036807896</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>29.6846201766412</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2.18458503501239</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2.18458503501239</v>
+        <v>2.296615036807896</v>
       </c>
     </row>
     <row r="82">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>

--- a/data/Ascona/investment_decision/Ascona_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/Ascona_SFH_2005-2014_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,61 +441,61 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>21.63846974340451</v>
+        <v>5.961584826790996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,30 +509,30 @@
         <v>19408.05189577003</v>
       </c>
       <c r="F2" t="n">
-        <v>21.63846974340451</v>
+        <v>5.961584826790996</v>
       </c>
       <c r="G2" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="H2" t="n">
-        <v>21.63846974340451</v>
+        <v>5.961584826791001</v>
       </c>
       <c r="I2" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="J2" t="n">
-        <v>21.63846974340451</v>
+        <v>5.961584826790996</v>
       </c>
       <c r="K2" t="n">
         <v>19408.05189577003</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>109.5802098818709</v>
+        <v>30.70612855833791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,30 +546,30 @@
         <v>19408.05189577003</v>
       </c>
       <c r="F3" t="n">
-        <v>107.2993600100631</v>
+        <v>32.27465575679175</v>
       </c>
       <c r="G3" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="H3" t="n">
-        <v>109.5802098818709</v>
+        <v>30.7061285583379</v>
       </c>
       <c r="I3" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="J3" t="n">
-        <v>107.2993600100631</v>
+        <v>32.27465575679175</v>
       </c>
       <c r="K3" t="n">
         <v>19408.05189577003</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>109.7017482814657</v>
+        <v>94.88843739401975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,30 +583,30 @@
         <v>19408.05189577003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.7017482814657</v>
+        <v>94.88843739401977</v>
       </c>
       <c r="G4" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="H4" t="n">
-        <v>109.7017482814657</v>
+        <v>94.88843739401977</v>
       </c>
       <c r="I4" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="J4" t="n">
-        <v>109.7017482814657</v>
+        <v>94.88843739401979</v>
       </c>
       <c r="K4" t="n">
         <v>19408.05189577003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751408</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,30 +620,30 @@
         <v>19408.05189577003</v>
       </c>
       <c r="F5" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751407</v>
       </c>
       <c r="G5" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="H5" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751408</v>
       </c>
       <c r="I5" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="J5" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751407</v>
       </c>
       <c r="K5" t="n">
         <v>19408.05189577003</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751408</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,26 +657,26 @@
         <v>19408.05189577003</v>
       </c>
       <c r="F6" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751407</v>
       </c>
       <c r="G6" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="H6" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751408</v>
       </c>
       <c r="I6" t="n">
         <v>19408.05189577003</v>
       </c>
       <c r="J6" t="n">
-        <v>109.7017482814657</v>
+        <v>104.7943138751407</v>
       </c>
       <c r="K6" t="n">
         <v>19408.05189577003</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -683,36 +684,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ascona_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ascona_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>16.578148974153</v>
+        <v>55.72609078651686</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>29.11207784365505</v>
+        <v>31.73375118627613</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>29.11207784365505</v>
+        <v>31.73375118627613</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16.578148974153</v>
+        <v>55.72609078651686</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -720,36 +721,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ascona_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ascona_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>20.18031800472211</v>
+        <v>55.72609078651686</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>29.11207784365505</v>
+        <v>38.62899238149103</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>29.11207784365505</v>
+        <v>38.62899238149103</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20.18031800472211</v>
+        <v>55.72609078651686</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -757,36 +758,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ascona_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ascona_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>21.65587507166034</v>
+        <v>55.72609078651686</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>29.11207784365505</v>
+        <v>41.4534911175305</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>29.11207784365505</v>
+        <v>41.4534911175305</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21.65587507166034</v>
+        <v>55.72609078651686</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -794,36 +795,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ascona_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ascona_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>22.44462784992312</v>
+        <v>55.72609078651686</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>29.11207784365505</v>
+        <v>42.96331494960605</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>29.11207784365505</v>
+        <v>42.96331494960605</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.44462784992312</v>
+        <v>55.72609078651686</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -831,36 +832,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ascona_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ascona_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>22.93749663065686</v>
+        <v>55.72609078651686</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>29.11207784365505</v>
+        <v>43.90676016050826</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>29.11207784365505</v>
+        <v>43.90676016050826</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>22.93749663065686</v>
+        <v>55.72609078651686</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -897,7 +898,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -934,11 +935,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,30 +990,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,26 +1027,26 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009002339237647058</v>
+        <v>0.009377436705882352</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1082,7 +1083,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
@@ -1119,11 +1120,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="G19" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351712</v>
       </c>
       <c r="I19" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J19" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="K19" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F20" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="G20" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351712</v>
       </c>
       <c r="I20" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J20" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="K20" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F21" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="G21" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351712</v>
       </c>
       <c r="I21" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.181033780000001</v>
+        <v>2.510903180351713</v>
       </c>
       <c r="K21" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,11 +1490,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,30 +1508,30 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="G29" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.670130599648289</v>
       </c>
       <c r="I29" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="K29" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,30 +1545,30 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="G30" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.670130599648289</v>
       </c>
       <c r="I30" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="K30" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,26 +1582,26 @@
         <v>6.695489808000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="G31" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.670130599648289</v>
       </c>
       <c r="I31" t="n">
         <v>6.695489808000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.670130599648288</v>
       </c>
       <c r="K31" t="n">
         <v>6.695489808000001</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1985,29 +1986,29 @@
         <v>0.01</v>
       </c>
       <c r="E42" t="n">
+        <v>22.06667889117543</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>12.79481137712283</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>12.79481137712283</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>22.06667889117543</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>22.06667889117543</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>12.79481137712283</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2022,29 +2023,29 @@
         <v>0.01</v>
       </c>
       <c r="E43" t="n">
+        <v>22.06667889117543</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>15.55641955585784</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15.55641955585784</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>22.06667889117543</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>22.06667889117543</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>15.55641955585784</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2059,29 +2060,29 @@
         <v>0.01</v>
       </c>
       <c r="E44" t="n">
+        <v>22.06667889117543</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
         <v>16.69372711176654</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>16.69372711176654</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>22.06667889117543</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>22.06667889117543</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>16.69372711176654</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2096,29 +2097,29 @@
         <v>0.01</v>
       </c>
       <c r="E45" t="n">
+        <v>22.06667889117543</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>17.31024064161294</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>17.31024064161294</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>22.06667889117543</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>22.06667889117543</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17.31024064161294</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2133,29 +2134,29 @@
         <v>0.01</v>
       </c>
       <c r="E46" t="n">
+        <v>22.06667889117543</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
         <v>17.7020365223083</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>17.7020365223083</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>22.06667889117543</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>22.06667889117543</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>17.7020365223083</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2192,7 +2193,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2266,7 +2267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2340,7 +2341,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2355,29 +2356,29 @@
         <v>0.017</v>
       </c>
       <c r="E52" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>9.791321608834714</v>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>31.20690839082792</v>
+        <v>9.791321608834714</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>9.791321608834714</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
@@ -2392,33 +2393,33 @@
         <v>0.017</v>
       </c>
       <c r="E53" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
         <v>12.88031855625539</v>
       </c>
-      <c r="F53" t="n">
-        <v>0.4540405107664842</v>
-      </c>
-      <c r="G53" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>31.20690839082792</v>
+        <v>12.88031855625539</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4540405107664842</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>12.88031855625539</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>6.074260917059727</v>
+        <v>7.285621841408566</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,33 +2430,33 @@
         <v>0.017</v>
       </c>
       <c r="E54" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.639285871861427</v>
+      </c>
+      <c r="G54" t="n">
         <v>14.25692762004364</v>
       </c>
-      <c r="F54" t="n">
-        <v>6.510329549934112</v>
-      </c>
-      <c r="G54" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H54" t="n">
-        <v>6.074260917059727</v>
+        <v>7.285621841408567</v>
       </c>
       <c r="I54" t="n">
-        <v>31.20690839082792</v>
+        <v>14.25692762004364</v>
       </c>
       <c r="J54" t="n">
-        <v>6.510329549934112</v>
+        <v>6.639285871861427</v>
       </c>
       <c r="K54" t="n">
-        <v>14.25692762004364</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>6.728574331135669</v>
+        <v>7.548769997799013</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,33 +2467,33 @@
         <v>0.017</v>
       </c>
       <c r="E55" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7.100132599998234</v>
+      </c>
+      <c r="G55" t="n">
         <v>14.99985363935659</v>
       </c>
-      <c r="F55" t="n">
-        <v>7.040347518358541</v>
-      </c>
-      <c r="G55" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H55" t="n">
-        <v>6.728574331135669</v>
+        <v>7.548769997799015</v>
       </c>
       <c r="I55" t="n">
-        <v>31.20690839082792</v>
+        <v>14.99985363935659</v>
       </c>
       <c r="J55" t="n">
-        <v>7.040347518358541</v>
+        <v>7.100132599998232</v>
       </c>
       <c r="K55" t="n">
-        <v>14.99985363935659</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>7.126228968529673</v>
+        <v>7.548769997799013</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,29 +2504,29 @@
         <v>0.017</v>
       </c>
       <c r="E56" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7.100132599998234</v>
+      </c>
+      <c r="G56" t="n">
         <v>15.45846662840667</v>
       </c>
-      <c r="F56" t="n">
-        <v>7.606583658544579</v>
-      </c>
-      <c r="G56" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H56" t="n">
-        <v>7.126228968529673</v>
+        <v>7.548769997799015</v>
       </c>
       <c r="I56" t="n">
-        <v>31.20690839082792</v>
+        <v>15.45846662840667</v>
       </c>
       <c r="J56" t="n">
-        <v>7.606583658544579</v>
+        <v>7.100132599998232</v>
       </c>
       <c r="K56" t="n">
-        <v>15.45846662840667</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,29 +2541,29 @@
         <v>0.017</v>
       </c>
       <c r="E57" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
         <v>9.791321608834714</v>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>31.20690839082792</v>
+        <v>9.791321608834714</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>9.791321608834714</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,29 +2578,29 @@
         <v>0.017</v>
       </c>
       <c r="E58" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>12.88031855625539</v>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>31.20690839082792</v>
+        <v>12.88031855625539</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>12.88031855625539</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,29 +2615,29 @@
         <v>0.017</v>
       </c>
       <c r="E59" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
         <v>14.25692762004364</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>31.20690839082792</v>
+        <v>14.25692762004364</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>14.25692762004364</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,29 +2652,29 @@
         <v>0.017</v>
       </c>
       <c r="E60" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>14.99985363935659</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>31.20690839082792</v>
+        <v>14.99985363935659</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>14.99985363935659</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,29 +2689,29 @@
         <v>0.017</v>
       </c>
       <c r="E61" t="n">
+        <v>31.20690839082792</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
         <v>15.45846662840667</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>31.20690839082792</v>
-      </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>31.20690839082792</v>
+        <v>15.45846662840667</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>15.45846662840667</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2747,11 +2748,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.5663190004483585</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2771,7 +2772,7 @@
         <v>31.20690839082792</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5663190004483585</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>31.20690839082792</v>
@@ -2784,11 +2785,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>6.489377089279921</v>
+        <v>1.813826343894882</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,30 +2803,30 @@
         <v>31.20690839082792</v>
       </c>
       <c r="F64" t="n">
-        <v>5.890717101904373</v>
+        <v>2.513245298677732</v>
       </c>
       <c r="G64" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H64" t="n">
-        <v>6.489377089279921</v>
+        <v>1.81382634389488</v>
       </c>
       <c r="I64" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J64" t="n">
-        <v>5.890717101904373</v>
+        <v>2.513245298677731</v>
       </c>
       <c r="K64" t="n">
         <v>31.20690839082792</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>7.835063675203981</v>
+        <v>3.274253949235158</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,30 +2840,30 @@
         <v>31.20690839082792</v>
       </c>
       <c r="F65" t="n">
-        <v>7.360699133479946</v>
+        <v>3.775974332271654</v>
       </c>
       <c r="G65" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H65" t="n">
-        <v>7.835063675203981</v>
+        <v>3.274253949235157</v>
       </c>
       <c r="I65" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J65" t="n">
-        <v>7.360699133479946</v>
+        <v>3.775974332271655</v>
       </c>
       <c r="K65" t="n">
         <v>31.20690839082792</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>9.545675405931656</v>
+        <v>3.401021840988245</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,26 +2877,26 @@
         <v>31.20690839082792</v>
       </c>
       <c r="F66" t="n">
-        <v>9.065320715916751</v>
+        <v>3.849659238789025</v>
       </c>
       <c r="G66" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H66" t="n">
-        <v>9.545675405931656</v>
+        <v>3.401021840988244</v>
       </c>
       <c r="I66" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J66" t="n">
-        <v>9.065320715916751</v>
+        <v>3.849659238789026</v>
       </c>
       <c r="K66" t="n">
         <v>31.20690839082792</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2932,7 +2933,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2969,7 +2970,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3006,7 +3007,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3080,7 +3081,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,7 +3096,7 @@
         <v>0.017</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9658235990298158</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3113,11 +3114,11 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9658235990298158</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,7 +3133,7 @@
         <v>0.017</v>
       </c>
       <c r="E73" t="n">
-        <v>1.495821401433555</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3150,11 +3151,11 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.495821401433555</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,7 +3170,7 @@
         <v>0.017</v>
       </c>
       <c r="E74" t="n">
-        <v>1.845230926841906</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3187,11 +3188,11 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.845230926841906</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,7 +3207,7 @@
         <v>0.017</v>
       </c>
       <c r="E75" t="n">
-        <v>2.09966409142957</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3224,11 +3225,11 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2.09966409142957</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,7 +3244,7 @@
         <v>0.017</v>
       </c>
       <c r="E76" t="n">
-        <v>2.296615036807896</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3261,11 +3262,11 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2.296615036807896</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3280,7 +3281,7 @@
         <v>0.017</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9658235990298158</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3298,15 +3299,15 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9658235990298158</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530863</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,33 +3318,33 @@
         <v>0.017</v>
       </c>
       <c r="E78" t="n">
-        <v>1.495821401433555</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F78" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737528</v>
       </c>
       <c r="G78" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530865</v>
       </c>
       <c r="I78" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J78" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737535</v>
       </c>
       <c r="K78" t="n">
-        <v>1.495821401433555</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530863</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,33 +3355,33 @@
         <v>0.017</v>
       </c>
       <c r="E79" t="n">
-        <v>1.845230926841906</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F79" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737526</v>
       </c>
       <c r="G79" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530865</v>
       </c>
       <c r="I79" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J79" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737535</v>
       </c>
       <c r="K79" t="n">
-        <v>1.845230926841906</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530863</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3391,29 +3392,29 @@
         <v>0.017</v>
       </c>
       <c r="E80" t="n">
-        <v>2.09966409142957</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F80" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737526</v>
       </c>
       <c r="G80" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9060942968012863</v>
+        <v>0.1267678917530865</v>
       </c>
       <c r="I80" t="n">
         <v>31.20690839082792</v>
       </c>
       <c r="J80" t="n">
-        <v>1.068685651302448</v>
+        <v>0.07368490651737535</v>
       </c>
       <c r="K80" t="n">
-        <v>2.09966409142957</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,7 +3429,7 @@
         <v>0.017</v>
       </c>
       <c r="E81" t="n">
-        <v>2.296615036807896</v>
+        <v>31.20690839082792</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3446,11 +3447,11 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2.296615036807896</v>
+        <v>31.20690839082792</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3463,29 +3464,29 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
         <v>0.4293250562242569</v>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3498,29 +3499,29 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
         <v>0.5615523961267772</v>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3533,29 +3534,29 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
         <v>0.624556919057325</v>
       </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3568,29 +3569,29 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
         <v>0.6622379613453093</v>
       </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3603,29 +3604,29 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
         <v>0.6881588528152967</v>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3638,29 +3639,29 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
         <v>0.4293250562242569</v>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3673,29 +3674,29 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
         <v>0.5615523961267772</v>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3708,29 +3709,29 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
         <v>0.624556919057325</v>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3743,29 +3744,29 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
         <v>0.6622379613453093</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3778,29 +3779,29 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>0.6881588528152967</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3813,29 +3814,29 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
         <v>0.4293250562242569</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.4293250562242569</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.4293250562242569</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3848,29 +3849,29 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
         <v>0.5615523961267772</v>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.5615523961267772</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.5615523961267772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3883,29 +3884,29 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
         <v>0.624556919057325</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.624556919057325</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.624556919057325</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3918,29 +3919,29 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
         <v>0.6622379613453093</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0.6622379613453093</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6622379613453093</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3953,25 +3954,25 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
         <v>0.6881588528152967</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.6881588528152967</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6881588528152967</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
